--- a/public/data/hourly_hits.xlsx
+++ b/public/data/hourly_hits.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:55</t>
+          <t>2026-08-10 17:22</t>
         </is>
       </c>
     </row>

--- a/public/data/hourly_hits.xlsx
+++ b/public/data/hourly_hits.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INDUSINDBK.NS</t>
+          <t>NAUKRI.NS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAUKRI.NS</t>
+          <t>JSWDULUX.NS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JSWDULUX.NS</t>
+          <t>JSWENERGY.NS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JSWENERGY.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>JUBLFOOD.NS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JUBLFOOD.NS</t>
+          <t>KPRMILL.NS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KPRMILL.NS</t>
+          <t>KEI.NS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KEI.NS</t>
+          <t>KPIL.NS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KPIL.NS</t>
+          <t>KIMS.NS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KIMS.NS</t>
+          <t>LTM.NS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LTM.NS</t>
+          <t>LT.NS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LT.NS</t>
+          <t>LENSKART.NS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LENSKART.NS</t>
+          <t>M&amp;MFIN.NS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>M&amp;MFIN.NS</t>
+          <t>M&amp;M.NS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>M&amp;M.NS</t>
+          <t>MANAPPURAM.NS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MANAPPURAM.NS</t>
+          <t>MARUTI.NS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MARUTI.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>MPHASIS.NS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MPHASIS.NS</t>
+          <t>NSLNISP.NS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NSLNISP.NS</t>
+          <t>NEWGEN.NS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NEWGEN.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>OFSS.NS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OFSS.NS</t>
+          <t>PTCIL.NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PTCIL.NS</t>
+          <t>PIDILITIND.NS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PIDILITIND.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>RBLBANK.NS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RBLBANK.NS</t>
+          <t>RITES.NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RITES.NS</t>
+          <t>RADICO.NS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RADICO.NS</t>
+          <t>RELIANCE.NS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RELIANCE.NS</t>
+          <t>SCHNEIDER.NS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SCHNEIDER.NS</t>
+          <t>SHRIRAMFIN.NS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN.NS</t>
+          <t>SOLARINDS.NS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>SUMICHEM.NS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SUMICHEM.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TVSMOTOR.NS</t>
+          <t>TATACONSUM.NS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TATACONSUM.NS</t>
+          <t>TATAPOWER.NS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TATAPOWER.NS</t>
+          <t>TATATECH.NS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TATATECH.NS</t>
+          <t>TECHNOE.NS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NIACL.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>UNOMINDA.NS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UNOMINDA.NS</t>
+          <t>VIJAYA.NS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2555,19 +2555,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VIJAYA.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DIXON.NS</t>
+          <t>ABCAPITAL.NS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ELGIEQUIP.NS</t>
+          <t>DIXON.NS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>INDHOTEL.NS</t>
+          <t>ELGIEQUIP.NS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PRESTIGE.NS</t>
+          <t>INDHOTEL.NS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3237,19 +3237,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>APLAPOLLO.NS</t>
+          <t>PRESTIGE.NS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CPPLUS.NS</t>
+          <t>APLAPOLLO.NS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ABDL.NS</t>
+          <t>CPPLUS.NS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ANANDRATHI.NS</t>
+          <t>ABDL.NS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>ANANDRATHI.NS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APARINDS.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AUROPHARMA.NS</t>
+          <t>APARINDS.NS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DMART.NS</t>
+          <t>AUROPHARMA.NS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BEML.NS</t>
+          <t>DMART.NS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BALKRISIND.NS</t>
+          <t>BEML.NS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>BALKRISIND.NS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BELRISE.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BDL.NS</t>
+          <t>BELRISE.NS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BOSCHLTD.NS</t>
+          <t>BDL.NS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BRIGADE.NS</t>
+          <t>BOSCHLTD.NS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BRITANNIA.NS</t>
+          <t>BRIGADE.NS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CRISIL.NS</t>
+          <t>BRITANNIA.NS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CAPLIPOINT.NS</t>
+          <t>CRISIL.NS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CARBORUNIV.NS</t>
+          <t>CAPLIPOINT.NS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CEATLTD.NS</t>
+          <t>CARBORUNIV.NS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CHOICEIN.NS</t>
+          <t>CEATLTD.NS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CLEAN.NS</t>
+          <t>CHOICEIN.NS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>CLEAN.NS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CONCORDBIO.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>COROMANDEL.NS</t>
+          <t>CONCORDBIO.NS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DEEPAKNTR.NS</t>
+          <t>COROMANDEL.NS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DEVYANI.NS</t>
+          <t>DEEPAKNTR.NS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>DEVYANI.NS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EMCURE.NS</t>
+          <t>LALPATHLAB.NS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENDURANCE.NS</t>
+          <t>EMCURE.NS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENGINERSIN.NS</t>
+          <t>ENDURANCE.NS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EXIDEIND.NS</t>
+          <t>ENGINERSIN.NS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FEDERALBNK.NS</t>
+          <t>EXIDEIND.NS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>FEDERALBNK.NS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GLAXO.NS</t>
+          <t>GLAND.NS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MEDANTA.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GRASIM.NS</t>
+          <t>MEDANTA.NS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HEROMOTOCO.NS</t>
+          <t>GRASIM.NS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HINDALCO.NS</t>
+          <t>HEROMOTOCO.NS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>POWERINDIA.NS</t>
+          <t>HINDALCO.NS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HONASA.NS</t>
+          <t>POWERINDIA.NS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>HONASA.NS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IIFL.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>INDGN.NS</t>
+          <t>IIFL.NS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>INDIANB.NS</t>
+          <t>INDGN.NS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NAUKRI.NS</t>
+          <t>INDIANB.NS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JSWENERGY.NS</t>
+          <t>NAUKRI.NS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>JSWENERGY.NS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUBLFOOD.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KEI.NS</t>
+          <t>JUBLFOOD.NS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>KEI.NS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LTFOODS.NS</t>
+          <t>KALYANKJIL.NS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LTM.NS</t>
+          <t>LTFOODS.NS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LT.NS</t>
+          <t>LTM.NS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LENSKART.NS</t>
+          <t>LT.NS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>M&amp;MFIN.NS</t>
+          <t>LENSKART.NS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>M&amp;M.NS</t>
+          <t>M&amp;MFIN.NS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>M&amp;M.NS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TEGA.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>RAMCOCEM.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>TRAVELFOOD.NS</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TRAVELFOOD.NS</t>
+          <t>UNOMINDA.NS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>UNOMINDA.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5283,19 +5283,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Short Term Breakout</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>VEDL.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>ENDURANCE.NS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ENDURANCE.NS</t>
+          <t>GRASIM.NS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>GRASIM.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>PPLPHARMA.NS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PPLPHARMA.NS</t>
+          <t>RKFORGE.NS</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RKFORGE.NS</t>
+          <t>SAILIFE.NS</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5437,19 +5437,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Short Term Breakout</t>
+          <t>Potential Breakout</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SAILIFE.NS</t>
+          <t>APARINDS.NS</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5459,19 +5459,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Potential Breakout</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>APARINDS.NS</t>
+          <t>BRIGADE.NS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>BRIGADE.NS</t>
+          <t>NAUKRI.NS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NAUKRI.NS</t>
+          <t>NEWGEN.NS</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5722,14 +5722,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>NEWGEN.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5739,14 +5739,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POLYMED.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SAILIFE.NS</t>
+          <t>POLYMED.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5773,14 +5773,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SUMICHEM.NS</t>
+          <t>SAILIFE.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5790,14 +5790,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RAMCOCEM.NS</t>
+          <t>SUMICHEM.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5807,24 +5807,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>RAMCOCEM.NS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TITAN.NS</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5889,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5906,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5923,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5940,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5957,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5974,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5991,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -5989,7 +6006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6022,7 +6039,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6056,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6073,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6090,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6107,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6124,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6141,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6158,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6192,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6209,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6226,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6243,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6260,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6277,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6294,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6311,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6328,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6345,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6362,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6379,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6396,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6413,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6430,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6447,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6464,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6481,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6498,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6515,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6532,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6549,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6566,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6583,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6600,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6617,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6634,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6651,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6668,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6685,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6702,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6719,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6736,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6753,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6770,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6787,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -6787,14 +6804,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INDUSINDBK.NS</t>
+          <t>NAUKRI.NS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6804,14 +6821,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NAUKRI.NS</t>
+          <t>JSWDULUX.NS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6821,14 +6838,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JSWDULUX.NS</t>
+          <t>JSWENERGY.NS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6838,14 +6855,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JSWENERGY.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6855,14 +6872,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>JUBLFOOD.NS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6872,14 +6889,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JUBLFOOD.NS</t>
+          <t>KPRMILL.NS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6889,14 +6906,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KPRMILL.NS</t>
+          <t>KEI.NS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6906,14 +6923,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KEI.NS</t>
+          <t>KPIL.NS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6923,14 +6940,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KPIL.NS</t>
+          <t>KIMS.NS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6940,14 +6957,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KIMS.NS</t>
+          <t>LTM.NS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6957,14 +6974,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LTM.NS</t>
+          <t>LT.NS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6974,14 +6991,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LT.NS</t>
+          <t>LENSKART.NS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6991,14 +7008,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LENSKART.NS</t>
+          <t>M&amp;MFIN.NS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7008,14 +7025,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M&amp;MFIN.NS</t>
+          <t>M&amp;M.NS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7025,14 +7042,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>M&amp;M.NS</t>
+          <t>MANAPPURAM.NS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7042,14 +7059,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MANAPPURAM.NS</t>
+          <t>MARUTI.NS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7059,14 +7076,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MARUTI.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7076,14 +7093,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>MPHASIS.NS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7093,14 +7110,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MPHASIS.NS</t>
+          <t>NSLNISP.NS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7110,14 +7127,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NSLNISP.NS</t>
+          <t>NEWGEN.NS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7127,14 +7144,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NEWGEN.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7144,14 +7161,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>OFSS.NS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7161,14 +7178,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OFSS.NS</t>
+          <t>PTCIL.NS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7178,14 +7195,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PTCIL.NS</t>
+          <t>PIDILITIND.NS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7195,14 +7212,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PIDILITIND.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7212,14 +7229,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>RBLBANK.NS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7229,14 +7246,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RBLBANK.NS</t>
+          <t>RITES.NS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7246,14 +7263,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RITES.NS</t>
+          <t>RADICO.NS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7263,14 +7280,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RADICO.NS</t>
+          <t>RELIANCE.NS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7280,14 +7297,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RELIANCE.NS</t>
+          <t>SCHNEIDER.NS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7297,14 +7314,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SCHNEIDER.NS</t>
+          <t>SHRIRAMFIN.NS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7314,14 +7331,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN.NS</t>
+          <t>SOLARINDS.NS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7331,14 +7348,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>SUMICHEM.NS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7348,14 +7365,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUMICHEM.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7365,14 +7382,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7382,14 +7399,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TVSMOTOR.NS</t>
+          <t>TATACONSUM.NS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7399,14 +7416,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TATACONSUM.NS</t>
+          <t>TATAPOWER.NS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7416,14 +7433,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TATAPOWER.NS</t>
+          <t>TATATECH.NS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7433,14 +7450,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TATATECH.NS</t>
+          <t>TECHNOE.NS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7450,14 +7467,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7467,14 +7484,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NIACL.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7484,14 +7501,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>UNOMINDA.NS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7501,14 +7518,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>UNOMINDA.NS</t>
+          <t>VIJAYA.NS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7518,24 +7535,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>VIJAYA.NS</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BELRISE.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7600,14 +7600,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM.NS</t>
+          <t>BELRISE.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7617,14 +7617,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEROMOTOCO.NS</t>
+          <t>GRASIM.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7634,14 +7634,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDGN.NS</t>
+          <t>HEROMOTOCO.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7651,14 +7651,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAUKRI.NS</t>
+          <t>INDGN.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7668,14 +7668,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>NAUKRI.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JUBLFOOD.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LENSKART.NS</t>
+          <t>JUBLFOOD.NS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7719,14 +7719,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>LENSKART.NS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7736,14 +7736,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OIL.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>OIL.NS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7770,14 +7770,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PPLPHARMA.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7787,14 +7787,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RHIM.NS</t>
+          <t>PPLPHARMA.NS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RKFORGE.NS</t>
+          <t>RHIM.NS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7821,14 +7821,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAILIFE.NS</t>
+          <t>RKFORGE.NS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7838,14 +7838,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUMICHEM.NS</t>
+          <t>SAILIFE.NS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>SUMICHEM.NS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7872,24 +7872,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>SYRMA.NS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>TITAN.NS</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7954,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7971,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7988,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -7988,7 +8005,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8022,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8039,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8056,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8077,7 +8094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DIXON.NS</t>
+          <t>ABCAPITAL.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8087,14 +8104,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELGIEQUIP.NS</t>
+          <t>DIXON.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8104,14 +8121,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDHOTEL.NS</t>
+          <t>ELGIEQUIP.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8121,24 +8138,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>INDHOTEL.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>PRESTIGE.NS</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8186,7 +8220,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8237,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8254,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8271,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8288,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8305,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8322,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8339,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8356,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8373,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8390,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8407,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8424,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8441,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8458,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8492,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8509,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8526,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8543,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8560,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8577,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8594,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8611,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8628,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8645,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8662,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8679,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8696,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8713,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8730,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8747,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8764,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8781,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8798,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8815,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8832,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8849,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8866,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8883,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8900,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8917,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8934,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8951,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8968,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8985,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8968,7 +9002,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -8985,7 +9019,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9036,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9053,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9070,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9087,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9104,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9121,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9138,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9155,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9172,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9189,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9206,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9189,14 +9223,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>MINDACORP.NS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9206,14 +9240,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MINDACORP.NS</t>
+          <t>MPHASIS.NS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9223,14 +9257,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MPHASIS.NS</t>
+          <t>NCC.NS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9240,14 +9274,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NCC.NS</t>
+          <t>OIL.NS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9257,14 +9291,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OIL.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9274,14 +9308,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>PGEL.NS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9291,14 +9325,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PGEL.NS</t>
+          <t>PTCIL.NS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9308,14 +9342,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PTCIL.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9325,14 +9359,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9342,14 +9376,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>PPLPHARMA.NS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9359,14 +9393,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PPLPHARMA.NS</t>
+          <t>POLYMED.NS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9376,14 +9410,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>POLYMED.NS</t>
+          <t>RHIM.NS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9393,14 +9427,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RHIM.NS</t>
+          <t>RKFORGE.NS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9410,14 +9444,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RKFORGE.NS</t>
+          <t>RELIANCE.NS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9427,14 +9461,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RELIANCE.NS</t>
+          <t>MOTHERSON.NS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9444,14 +9478,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MOTHERSON.NS</t>
+          <t>SAPPHIRE.NS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9461,14 +9495,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SAPPHIRE.NS</t>
+          <t>SCHNEIDER.NS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9478,14 +9512,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHNEIDER.NS</t>
+          <t>ENRIN.NS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9495,14 +9529,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENRIN.NS</t>
+          <t>SIGNATURE.NS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9512,14 +9546,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SIGNATURE.NS</t>
+          <t>SUMICHEM.NS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9529,14 +9563,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUMICHEM.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9546,14 +9580,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9563,14 +9597,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TVSMOTOR.NS</t>
+          <t>TATACONSUM.NS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9580,14 +9614,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TATACONSUM.NS</t>
+          <t>TATAELXSI.NS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9597,14 +9631,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TATAELXSI.NS</t>
+          <t>TATAINVEST.NS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9614,14 +9648,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TATAINVEST.NS</t>
+          <t>TATATECH.NS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9631,14 +9665,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TATATECH.NS</t>
+          <t>TECHNOE.NS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9648,14 +9682,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9665,14 +9699,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TEGA.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9682,14 +9716,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RAMCOCEM.NS</t>
+          <t>TRAVELFOOD.NS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9699,14 +9733,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>UNOMINDA.NS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9716,14 +9750,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TRAVELFOOD.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9733,41 +9767,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>UNOMINDA.NS</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-10 17:22</t>
+          <t>2026-08-10 17:29</t>
         </is>
       </c>
     </row>

--- a/public/data/hourly_hits.xlsx
+++ b/public/data/hourly_hits.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GODREJCP.NS</t>
+          <t>CAPLIPOINT.NS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GRANULES.NS</t>
+          <t>COALINDIA.NS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -510,19 +510,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Option Sell (Chirag)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ABB.NS</t>
+          <t>THERMAX.NS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APLAPOLLO.NS</t>
+          <t>ABB.NS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AARTIIND.NS</t>
+          <t>APLAPOLLO.NS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACE.NS</t>
+          <t>AARTIIND.NS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADANIENT.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ABSLAMC.NS</t>
+          <t>CPPLUS.NS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CPPLUS.NS</t>
+          <t>AFCONS.NS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AFCONS.NS</t>
+          <t>ANANDRATHI.NS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANANDRATHI.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>ASHOKLEY.NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASHOKLEY.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CRISIL.NS</t>
+          <t>BRIGADE.NS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CANBK.NS</t>
+          <t>CRISIL.NS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>CARTRADE.NS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHOLAFIN.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLEAN.NS</t>
+          <t>COHANCE.NS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COHANCE.NS</t>
+          <t>DALBHARAT.NS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONCOR.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DALBHARAT.NS</t>
+          <t>LALPATHLAB.NS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DIVISLAB.NS</t>
+          <t>FACT.NS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DRREDDY.NS</t>
+          <t>GLAND.NS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EICHERMOT.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMMVEE.NS</t>
+          <t>GPIL.NS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>GRASIM.NS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FACT.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>GMDCLTD.NS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GAIL.NS</t>
+          <t>HINDALCO.NS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GRASIM.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>INDGN.NS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FLUOROCHEM.NS</t>
+          <t>IREDA.NS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GMDCLTD.NS</t>
+          <t>JMFINANCIL.NS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HINDALCO.NS</t>
+          <t>JSWINFRA.NS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INDGN.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INDIANB.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JMFINANCIL.NS</t>
+          <t>KFINTECH.NS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JSWINFRA.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>LTF.NS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>LICHSGFIN.NS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>MFSL.NS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KFINTECH.NS</t>
+          <t>MUTHOOTFIN.NS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTF.NS</t>
+          <t>NATIONALUM.NS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LICHSGFIN.NS</t>
+          <t>NAVINFLUOR.NS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>NEULANDLAB.NS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MANAPPURAM.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MFSL.NS</t>
+          <t>PIRAMALFIN.NS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MOTILALOFS.NS</t>
+          <t>SAILIFE.NS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>SARDAEN.NS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN.NS</t>
+          <t>SHYAMMETL.NS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NATIONALUM.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAVINFLUOR.NS</t>
+          <t>TMCV.NS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NEULANDLAB.NS</t>
+          <t>TATASTEEL.NS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>UPL.NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>VTL.NS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2160,19 +2160,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PHOENIXLTD.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2182,19 +2182,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PIRAMALFIN.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2226,19 +2226,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2248,19 +2248,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAILIFE.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2270,19 +2270,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SARDAEN.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2292,19 +2292,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SHYAMMETL.NS</t>
+          <t>HINDCOPPER.NS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2314,19 +2314,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2336,19 +2336,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STARHEALTH.NS</t>
+          <t>HYUNDAI.NS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2358,19 +2358,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2380,19 +2380,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPLPETRO.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2402,19 +2402,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TMCV.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2424,19 +2424,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TATASTEEL.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2446,19 +2446,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2468,19 +2468,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RAMCOCEM.NS</t>
+          <t>KAYNES.NS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2490,19 +2490,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UNOMINDA.NS</t>
+          <t>LAURUSLABS.NS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2534,19 +2534,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UPL.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2556,19 +2556,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VTL.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Rathod Bullish</t>
+          <t>Momentum Scan</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VEDL.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>SBICARD.NS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HINDCOPPER.NS</t>
+          <t>UNIONBANK.NS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2710,19 +2710,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bullish</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2732,19 +2732,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bullish</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bullish</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>DALBHARAT.NS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2776,19 +2776,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bullish</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2798,19 +2798,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>BAJFINANCE.NS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2820,19 +2820,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>FIRSTCRY.NS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2842,19 +2842,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>GODREJCP.NS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2864,19 +2864,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>LINDEINDIA.NS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2886,19 +2886,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>Dual BB 15min Bearish</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>SCHAEFFLER.NS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2908,19 +2908,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>AWL.NS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2930,19 +2930,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>ADANIENT.NS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2952,19 +2952,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2974,19 +2974,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>ANGELONE.NS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3018,19 +3018,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>ASHOKLEY.NS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3040,19 +3040,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Momentum Scan</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UNIONBANK.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3062,19 +3062,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ADANIPORTS.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3084,19 +3084,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>BANKINDIA.NS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HFCL.NS</t>
+          <t>MAHABANK.NS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>BOSCHLTD.NS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3150,19 +3150,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>CGCL.NS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3172,19 +3172,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TMCV.NS</t>
+          <t>CEMPRO.NS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3194,19 +3194,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bullish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>CDSL.NS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3216,19 +3216,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Dual BB 15min Bearish</t>
+          <t>BullBhai Bullish Momentum</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BELRISE.NS</t>
+          <t>CHALET.NS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AUBANK.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AWL.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ADANIENT.NS</t>
+          <t>COHANCE.NS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ABSLAMC.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ABDL.NS</t>
+          <t>DEEPAKNTR.NS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AMBER.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ANGELONE.NS</t>
+          <t>LALPATHLAB.NS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>EMMVEE.NS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>APARINDS.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ASHOKLEY.NS</t>
+          <t>FACT.NS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BANKINDIA.NS</t>
+          <t>GLAND.NS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MAHABANK.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BHEL.NS</t>
+          <t>GLENMARK.NS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BOSCHLTD.NS</t>
+          <t>MEDANTA.NS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CDSL.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CHALET.NS</t>
+          <t>HDFCAMC.NS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>HYUNDAI.NS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>COHANCE.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DEEPAKNTR.NS</t>
+          <t>INDIANB.NS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DEVYANI.NS</t>
+          <t>IPCALAB.NS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DIVISLAB.NS</t>
+          <t>JMFINANCIL.NS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>JSWINFRA.NS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EICHERMOT.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EMMVEE.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FACT.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
+          <t>KALYANKJIL.NS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GLAXO.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GLENMARK.NS</t>
+          <t>KAYNES.NS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MEDANTA.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>LICHSGFIN.NS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FLUOROCHEM.NS</t>
+          <t>LAURUSLABS.NS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HDFCAMC.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HDFCLIFE.NS</t>
+          <t>MFSL.NS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HYUNDAI.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>INDIANB.NS</t>
+          <t>NEULANDLAB.NS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JMFINANCIL.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JSWINFRA.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>PNBHOUSING.NS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>PVRINOX.NS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>PIRAMALFIN.NS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>SAGILITY.NS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>SHYAMMETL.NS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LICHSGFIN.NS</t>
+          <t>SOLARINDS.NS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>STARHEALTH.NS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LODHA.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>SPLPETRO.NS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MOTILALOFS.NS</t>
+          <t>SYNGENE.NS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>TMCV.NS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NEULANDLAB.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>UPL.NS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PNBHOUSING.NS</t>
+          <t>UNIONBANK.NS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4712,19 +4712,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Short Term Breakout</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4734,19 +4734,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Short Term Breakout</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4756,19 +4756,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Short Term Breakout</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PIRAMALFIN.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4778,19 +4778,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Short Term Breakout</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RADICO.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4800,19 +4800,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Potential Breakout</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>ADANIENT.NS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4822,19 +4822,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Potential Breakout</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>CGCL.NS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4844,19 +4844,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Potential Breakout</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SAGILITY.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SHYAMMETL.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4910,19 +4910,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>STARHEALTH.NS</t>
+          <t>MEDANTA.NS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4932,19 +4932,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4954,19 +4954,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SPLPETRO.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SYNGENE.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4998,19 +4998,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5020,19 +5020,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TBOTEK.NS</t>
+          <t>NAVINFLUOR.NS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5042,19 +5042,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TVSMOTOR.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5064,19 +5064,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TMCV.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5086,19 +5086,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>100% Buy Breakout</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NIACL.NS</t>
+          <t>SAGILITY.NS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5108,19 +5108,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BullBhai Bullish Momentum</t>
+          <t>Possible Bottom Out (Weekly)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TITAN.NS</t>
+          <t>ANGELONE.NS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5130,425 +5130,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>BullBhai Bullish Momentum</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>UPL.NS</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>BullBhai Bullish Momentum</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>UNIONBANK.NS</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>BullBhai Bullish Momentum</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Short Term Breakout</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>CHALET.NS</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Short Term Breakout</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>CYIENT.NS</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Short Term Breakout</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>JINDALSAW.NS</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Short Term Breakout</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>JYOTICNC.NS</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Short Term Breakout</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>SAPPHIRE.NS</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Potential Breakout</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>ADANIENT.NS</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Potential Breakout</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>CGCL.NS</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>ANTHEM.NS</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>MEDANTA.NS</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>HINDZINC.NS</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>JINDALSAW.NS</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>NAVINFLUOR.NS</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>POLICYBZR.NS</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>SBFC.NS</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>100% Buy Breakout</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>SAGILITY.NS</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Possible Bottom Out (Weekly)</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>ANGELONE.NS</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5596,14 +5178,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MEDANTA.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5613,14 +5195,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>MEDANTA.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5630,14 +5212,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5647,14 +5229,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAVINFLUOR.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5664,14 +5246,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5681,14 +5263,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5698,24 +5280,75 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>NAVINFLUOR.NS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POLICYBZR.NS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBFC.NS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>SAGILITY.NS</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5396,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5801,7 +5434,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GODREJCP.NS</t>
+          <t>CAPLIPOINT.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5811,14 +5444,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRANULES.NS</t>
+          <t>COALINDIA.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5828,7 +5461,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5478,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>THERMAX.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5893,7 +5543,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5560,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -5927,14 +5577,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACE.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5944,14 +5594,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIENT.NS</t>
+          <t>CPPLUS.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5961,14 +5611,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABSLAMC.NS</t>
+          <t>AFCONS.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5978,14 +5628,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CPPLUS.NS</t>
+          <t>ANANDRATHI.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5995,14 +5645,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AFCONS.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6012,14 +5662,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANANDRATHI.NS</t>
+          <t>ASHOKLEY.NS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6029,14 +5679,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6046,14 +5696,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASHOKLEY.NS</t>
+          <t>AXISBANK.NS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6063,14 +5713,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AXISBANK.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6080,14 +5730,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG.NS</t>
+          <t>MAHABANK.NS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6097,14 +5747,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAHABANK.NS</t>
+          <t>BOSCHLTD.NS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6114,14 +5764,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BOSCHLTD.NS</t>
+          <t>BRIGADE.NS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6131,7 +5781,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -6148,14 +5798,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CANBK.NS</t>
+          <t>CARTRADE.NS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6165,14 +5815,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>CDSL.NS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6182,14 +5832,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CDSL.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6199,14 +5849,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHOLAFIN.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6216,14 +5866,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>COHANCE.NS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6233,14 +5883,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CLEAN.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6250,14 +5900,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>DALBHARAT.NS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6267,14 +5917,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COHANCE.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6284,14 +5934,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONCOR.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6301,14 +5951,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>LALPATHLAB.NS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6318,14 +5968,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DALBHARAT.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6335,14 +5985,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>FACT.NS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6352,14 +6002,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DIVISLAB.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6369,14 +6019,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>GLAND.NS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6386,14 +6036,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DRREDDY.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6403,14 +6053,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EICHERMOT.NS</t>
+          <t>GPIL.NS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6420,14 +6070,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EMMVEE.NS</t>
+          <t>GRASIM.NS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6437,14 +6087,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6454,14 +6104,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FACT.NS</t>
+          <t>GMDCLTD.NS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6471,14 +6121,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>HINDALCO.NS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6488,14 +6138,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GAIL.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6505,14 +6155,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6522,14 +6172,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRASIM.NS</t>
+          <t>INDGN.NS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6539,14 +6189,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>IREDA.NS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6556,14 +6206,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FLUOROCHEM.NS</t>
+          <t>JMFINANCIL.NS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6573,14 +6223,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GMDCLTD.NS</t>
+          <t>JSWINFRA.NS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6590,14 +6240,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDALCO.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6607,14 +6257,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6624,14 +6274,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6641,14 +6291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INDGN.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6658,14 +6308,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>INDIANB.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6675,14 +6325,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>KFINTECH.NS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6692,14 +6342,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JMFINANCIL.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6709,14 +6359,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JSWINFRA.NS</t>
+          <t>LTF.NS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6726,14 +6376,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>LICHSGFIN.NS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6743,14 +6393,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>MFSL.NS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6760,14 +6410,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6777,14 +6427,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6794,14 +6444,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6811,14 +6461,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>MUTHOOTFIN.NS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6828,14 +6478,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KFINTECH.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6845,14 +6495,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>NATIONALUM.NS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6862,14 +6512,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LTF.NS</t>
+          <t>NAVINFLUOR.NS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6879,14 +6529,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LICHSGFIN.NS</t>
+          <t>NEULANDLAB.NS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6896,14 +6546,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6913,14 +6563,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MANAPPURAM.NS</t>
+          <t>PIRAMALFIN.NS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6930,14 +6580,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MFSL.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6947,14 +6597,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>SAILIFE.NS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6964,14 +6614,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MOTILALOFS.NS</t>
+          <t>SARDAEN.NS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6981,14 +6631,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>SHYAMMETL.NS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6998,14 +6648,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7015,14 +6665,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7032,14 +6682,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NATIONALUM.NS</t>
+          <t>TMCV.NS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7049,14 +6699,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NAVINFLUOR.NS</t>
+          <t>TATASTEEL.NS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7066,14 +6716,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEULANDLAB.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7083,14 +6733,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>UPL.NS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7100,14 +6750,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>VTL.NS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7117,14 +6767,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7134,364 +6784,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>PARADEEP.NS</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD.NS</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PIRAMALFIN.NS</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SBFC.NS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>SBICARD.NS</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SAILIFE.NS</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>SARDAEN.NS</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>SHYAMMETL.NS</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SOLARINDS.NS</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STARHEALTH.NS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SAIL.NS</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SPLPETRO.NS</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TMCV.NS</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>TATASTEEL.NS</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TECHNOE.NS</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>RAMCOCEM.NS</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TITAN.NS</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>UNOMINDA.NS</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>UPL.NS</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>VTL.NS</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -7506,7 +6799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7539,7 +6832,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -7556,7 +6849,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -7573,7 +6866,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -7590,14 +6883,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HINDCOPPER.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7607,14 +6900,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7624,14 +6917,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>HINDCOPPER.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7641,14 +6934,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7658,14 +6951,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>HYUNDAI.NS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7675,14 +6968,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7692,14 +6985,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7709,14 +7002,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7726,14 +7019,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7743,14 +7036,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7760,14 +7053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>KAYNES.NS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7777,14 +7070,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7794,14 +7087,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>LAURUSLABS.NS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7811,14 +7104,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7828,14 +7121,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7845,14 +7138,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7862,24 +7155,92 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>PARADEEP.NS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SBFC.NS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SBICARD.NS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SAIL.NS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>UNIONBANK.NS</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7917,7 +7278,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPORTS.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7927,14 +7288,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7944,14 +7305,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HFCL.NS</t>
+          <t>DALBHARAT.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7961,14 +7322,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7978,58 +7339,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KALYANKJIL.NS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TMCV.NS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TITAN.NS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -8044,7 +7354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8067,7 +7377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BELRISE.NS</t>
+          <t>BAJFINANCE.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8077,7 +7387,75 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIRSTCRY.NS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GODREJCP.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LINDEINDIA.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER.NS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -8092,7 +7470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8115,7 +7493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUBANK.NS</t>
+          <t>AWL.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8125,14 +7503,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWL.NS</t>
+          <t>ADANIENT.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8142,14 +7520,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIENT.NS</t>
+          <t>ABSLAMC.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8159,14 +7537,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABSLAMC.NS</t>
+          <t>ANGELONE.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8176,14 +7554,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABDL.NS</t>
+          <t>ANTHEM.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8193,14 +7571,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMBER.NS</t>
+          <t>ASHOKLEY.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8210,14 +7588,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANGELONE.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8227,14 +7605,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANTHEM.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8244,14 +7622,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APARINDS.NS</t>
+          <t>BANKINDIA.NS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8261,14 +7639,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASHOKLEY.NS</t>
+          <t>MAHABANK.NS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8278,14 +7656,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BANKINDIA.NS</t>
+          <t>BOSCHLTD.NS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8295,14 +7673,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAHABANK.NS</t>
+          <t>CGCL.NS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8312,14 +7690,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHEL.NS</t>
+          <t>CEMPRO.NS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8329,14 +7707,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BOSCHLTD.NS</t>
+          <t>CDSL.NS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8346,14 +7724,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>CHALET.NS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8363,14 +7741,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CDSL.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8380,14 +7758,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHALET.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8397,14 +7775,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>COHANCE.NS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8414,14 +7792,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8431,14 +7809,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COHANCE.NS</t>
+          <t>DEEPAKNTR.NS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8448,14 +7826,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>DIVISLAB.NS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8465,14 +7843,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DEEPAKNTR.NS</t>
+          <t>LALPATHLAB.NS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8482,14 +7860,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEVYANI.NS</t>
+          <t>EMMVEE.NS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8499,14 +7877,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DIVISLAB.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8516,14 +7894,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LALPATHLAB.NS</t>
+          <t>FACT.NS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8533,14 +7911,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EICHERMOT.NS</t>
+          <t>GLAND.NS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8550,14 +7928,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EMMVEE.NS</t>
+          <t>GLAXO.NS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8567,14 +7945,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>GLENMARK.NS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8584,14 +7962,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FACT.NS</t>
+          <t>MEDANTA.NS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8601,14 +7979,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8618,14 +7996,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GLAXO.NS</t>
+          <t>FLUOROCHEM.NS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8635,14 +8013,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GLENMARK.NS</t>
+          <t>HDFCAMC.NS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8652,14 +8030,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MEDANTA.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8669,14 +8047,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>HYUNDAI.NS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8686,14 +8064,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLUOROCHEM.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8703,14 +8081,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HDFCAMC.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8720,14 +8098,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HDFCLIFE.NS</t>
+          <t>INDIANB.NS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8737,14 +8115,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>IPCALAB.NS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8754,14 +8132,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HYUNDAI.NS</t>
+          <t>JMFINANCIL.NS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8771,14 +8149,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>JSWINFRA.NS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8788,14 +8166,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>JSWSTEEL.NS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8805,14 +8183,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INDIANB.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8822,14 +8200,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>JINDALSTEL.NS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8839,14 +8217,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JMFINANCIL.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8856,14 +8234,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JSWINFRA.NS</t>
+          <t>KALYANKJIL.NS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8873,14 +8251,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JSWSTEEL.NS</t>
+          <t>KARURVYSYA.NS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8890,14 +8268,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>KAYNES.NS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8907,14 +8285,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JINDALSTEL.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8924,14 +8302,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>LICHSGFIN.NS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8941,14 +8319,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KALYANKJIL.NS</t>
+          <t>LAURUSLABS.NS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8958,14 +8336,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KARURVYSYA.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8975,14 +8353,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KAYNES.NS</t>
+          <t>MFSL.NS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8992,14 +8370,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>MAZDOCK.NS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9009,14 +8387,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LICHSGFIN.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9026,14 +8404,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LAURUSLABS.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9043,14 +8421,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LODHA.NS</t>
+          <t>NMDC.NS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9060,14 +8438,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MAZDOCK.NS</t>
+          <t>NEULANDLAB.NS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9077,14 +8455,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MOTILALOFS.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9094,14 +8472,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9111,14 +8489,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9128,14 +8506,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NMDC.NS</t>
+          <t>PNBHOUSING.NS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9145,14 +8523,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEULANDLAB.NS</t>
+          <t>PVRINOX.NS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9162,14 +8540,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9179,14 +8557,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9196,14 +8574,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>PIRAMALFIN.NS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9213,14 +8591,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PNBHOUSING.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9230,14 +8608,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>SAGILITY.NS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9247,14 +8625,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>SHYAMMETL.NS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9264,14 +8642,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>SOLARINDS.NS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9281,14 +8659,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PIRAMALFIN.NS</t>
+          <t>STARHEALTH.NS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9298,14 +8676,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RADICO.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9315,14 +8693,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>SPLPETRO.NS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9332,14 +8710,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>SYNGENE.NS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9349,14 +8727,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SAGILITY.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9366,14 +8744,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHYAMMETL.NS</t>
+          <t>TVSMOTOR.NS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9383,14 +8761,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>TMCV.NS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9400,14 +8778,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STARHEALTH.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9417,14 +8795,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9434,14 +8812,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SPLPETRO.NS</t>
+          <t>TITAN.NS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9451,14 +8829,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SYNGENE.NS</t>
+          <t>UPL.NS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9468,14 +8846,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>UNIONBANK.NS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9485,14 +8863,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TBOTEK.NS</t>
+          <t>VEDL.NS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9502,126 +8880,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TVSMOTOR.NS</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TMCV.NS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>NIACL.NS</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TITAN.NS</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>UPL.NS</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>UNIONBANK.NS</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>VEDL.NS</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -9636,7 +8895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9659,7 +8918,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHALET.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9669,14 +8928,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9686,14 +8945,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9703,14 +8962,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>MOTILALOFS.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9720,24 +8979,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAPPHIRE.NS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -9752,7 +8994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9785,7 +9027,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9044,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26 09:28</t>
+          <t>2026-08-26 11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRAVITA.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nifty 500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54</t>
         </is>
       </c>
     </row>
